--- a/backend/data/financials_by_company/000912.SZ.xlsx
+++ b/backend/data/financials_by_company/000912.SZ.xlsx
@@ -4265,10 +4265,8 @@
           <t>Luzhou</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>646300</t>
-        </is>
+      <c r="D2" t="n">
+        <v>646300</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4488,7 +4486,7 @@
         <v>31787198</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -4622,7 +4620,7 @@
         </is>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
         <v>-0.9970002</v>
